--- a/12 政治模型/img/excel 数据表.xlsx
+++ b/12 政治模型/img/excel 数据表.xlsx
@@ -9,17 +9,17 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="1830" windowWidth="12360" windowHeight="7620"/>
+    <workbookView xWindow="0" yWindow="3660" windowWidth="12360" windowHeight="7620"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="152511"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="35">
   <si>
     <t>国家</t>
   </si>
@@ -61,6 +61,74 @@
   </si>
   <si>
     <t>日本</t>
+  </si>
+  <si>
+    <t>前苏联地区</t>
+  </si>
+  <si>
+    <t>1500年</t>
+    <phoneticPr fontId="53" type="noConversion"/>
+  </si>
+  <si>
+    <t>1913年</t>
+    <phoneticPr fontId="53" type="noConversion"/>
+  </si>
+  <si>
+    <t>年份</t>
+    <phoneticPr fontId="53" type="noConversion"/>
+  </si>
+  <si>
+    <t>欧洲</t>
+  </si>
+  <si>
+    <t>西海岸 国家</t>
+  </si>
+  <si>
+    <t>拉丁美洲</t>
+  </si>
+  <si>
+    <t>亚洲</t>
+  </si>
+  <si>
+    <t>非洲</t>
+  </si>
+  <si>
+    <t>合计</t>
+  </si>
+  <si>
+    <t>其他</t>
+  </si>
+  <si>
+    <t>合计</t>
+    <phoneticPr fontId="53" type="noConversion"/>
+  </si>
+  <si>
+    <t>西海岸国家</t>
+    <phoneticPr fontId="53" type="noConversion"/>
+  </si>
+  <si>
+    <t>1820年</t>
+  </si>
+  <si>
+    <t>1870年</t>
+  </si>
+  <si>
+    <t>1950年</t>
+  </si>
+  <si>
+    <t>1973年</t>
+  </si>
+  <si>
+    <t>1998年</t>
+  </si>
+  <si>
+    <t>前苏联</t>
+  </si>
+  <si>
+    <t>中国</t>
+  </si>
+  <si>
+    <t>印度</t>
   </si>
 </sst>
 </file>
@@ -447,7 +515,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -457,6 +525,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor indexed="22"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -609,7 +683,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="70">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -667,7 +741,6 @@
     <xf numFmtId="0" fontId="50" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -775,6 +848,49 @@
     </xf>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1965,11 +2081,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="820735384"/>
-        <c:axId val="820736952"/>
+        <c:axId val="630887432"/>
+        <c:axId val="630887824"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="820735384"/>
+        <c:axId val="630887432"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2012,7 +2128,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="820736952"/>
+        <c:crossAx val="630887824"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2020,7 +2136,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="820736952"/>
+        <c:axId val="630887824"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2071,7 +2187,2790 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="820735384"/>
+        <c:crossAx val="630887432"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="zh-CN"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="zh-CN"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:date1904 val="0"/>
+  <c:lang val="zh-CN"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="zh-CN" altLang="zh-CN" sz="1200" b="0" i="0" baseline="0">
+                <a:effectLst/>
+              </a:rPr>
+              <a:t>英国与欧洲主要国家的</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" altLang="zh-CN" sz="1200" b="0" i="0" baseline="0">
+                <a:effectLst/>
+              </a:rPr>
+              <a:t>GDP</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="zh-CN" altLang="zh-CN" sz="1200" b="0" i="0" baseline="0">
+                <a:effectLst/>
+              </a:rPr>
+              <a:t>总量</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" altLang="zh-CN" sz="1200" b="0" i="0" baseline="0">
+                <a:effectLst/>
+              </a:rPr>
+              <a:t>:</a:t>
+            </a:r>
+            <a:br>
+              <a:rPr lang="en-US" altLang="zh-CN" sz="1200" b="0" i="0" baseline="0">
+                <a:effectLst/>
+              </a:rPr>
+            </a:br>
+            <a:r>
+              <a:rPr lang="en-US" altLang="zh-CN" sz="1200" b="0" i="0" baseline="0">
+                <a:effectLst/>
+              </a:rPr>
+              <a:t>1500—1913</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="zh-CN" altLang="zh-CN" sz="1200" b="0" i="0" baseline="0">
+                <a:effectLst/>
+              </a:rPr>
+              <a:t>年</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" altLang="zh-CN" sz="1200" b="0" i="0" baseline="0">
+                <a:effectLst/>
+              </a:rPr>
+              <a:t/>
+            </a:r>
+            <a:br>
+              <a:rPr lang="en-US" altLang="zh-CN" sz="1200" b="0" i="0" baseline="0">
+                <a:effectLst/>
+              </a:rPr>
+            </a:br>
+            <a:r>
+              <a:rPr lang="en-US" altLang="zh-CN" sz="1200" b="0" i="0" baseline="0">
+                <a:effectLst/>
+              </a:rPr>
+              <a:t>(</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="zh-CN" altLang="zh-CN" sz="1200" b="0" i="0" baseline="0">
+                <a:effectLst/>
+              </a:rPr>
+              <a:t>单位</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" altLang="zh-CN" sz="1200" b="0" i="0" baseline="0">
+                <a:effectLst/>
+              </a:rPr>
+              <a:t>:</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="zh-CN" altLang="zh-CN" sz="1200" b="0" i="0" baseline="0">
+                <a:effectLst/>
+              </a:rPr>
+              <a:t>百万</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" altLang="zh-CN" sz="1200" b="0" i="0" baseline="0">
+                <a:effectLst/>
+              </a:rPr>
+              <a:t>/1990</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="zh-CN" altLang="zh-CN" sz="1200" b="0" i="0" baseline="0">
+                <a:effectLst/>
+              </a:rPr>
+              <a:t>国际元</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" altLang="zh-CN" sz="1200" b="0" i="0" baseline="0">
+                <a:effectLst/>
+              </a:rPr>
+              <a:t>)</a:t>
+            </a:r>
+            <a:endParaRPr lang="zh-CN" altLang="zh-CN" sz="1200">
+              <a:effectLst/>
+            </a:endParaRPr>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="zh-CN"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet!$A$54</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>美国</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet!$B$53:$G$53</c:f>
+              <c:strCache>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>1500年</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1600</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1700</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1820</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1870</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1913年</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet!$B$54:$G$54</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>800</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>600</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>527</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>12548</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>98374</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>517383</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet!$A$55</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>德国</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet!$B$53:$G$53</c:f>
+              <c:strCache>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>1500年</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1600</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1700</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1820</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1870</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1913年</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet!$B$55:$G$55</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>8112</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>12432</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>13410</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>26349</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>71429</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>237332</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet!$A$56</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>前苏联地区</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent3"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet!$B$53:$G$53</c:f>
+              <c:strCache>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>1500年</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1600</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1700</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1820</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1870</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1913年</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet!$B$56:$G$56</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>8475</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>11447</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>16222</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>37710</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>83646</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>232351</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet!$A$57</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>英国</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="57150" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="bg2">
+                  <a:lumMod val="10000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:ln w="57150">
+                <a:solidFill>
+                  <a:schemeClr val="bg2">
+                    <a:lumMod val="10000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:dLbls>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="bg1"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="zh-CN"/>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:layout/>
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet!$B$53:$G$53</c:f>
+              <c:strCache>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>1500年</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1600</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1700</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1820</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1870</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1913年</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet!$B$57:$G$57</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>2815</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>6007</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>10709</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>36232</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>100719</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>224618</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="4"/>
+          <c:order val="4"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet!$A$58</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>法国</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent5"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent5"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent5"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet!$B$53:$G$53</c:f>
+              <c:strCache>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>1500年</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1600</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1700</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1820</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1870</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1913年</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet!$B$58:$G$58</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>10912</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>15559</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>21180</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>38434</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>72100</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>144489</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:marker val="1"/>
+        <c:smooth val="0"/>
+        <c:axId val="638333040"/>
+        <c:axId val="638333824"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="638333040"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="zh-CN"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="638333824"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="638333824"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:min val="100"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0.00&quot;万&quot;" sourceLinked="0"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="zh-CN"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="638333040"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+        <c:dispUnits>
+          <c:builtInUnit val="tenThousands"/>
+          <c:dispUnitsLbl>
+            <c:layout/>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="zh-CN"/>
+              </a:p>
+            </c:txPr>
+          </c:dispUnitsLbl>
+        </c:dispUnits>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="zh-CN"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="zh-CN"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:date1904 val="0"/>
+  <c:lang val="zh-CN"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" altLang="zh-CN"/>
+              <a:t>1914</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="zh-CN" altLang="en-US"/>
+              <a:t>年境外投资的现价总值</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-US" altLang="zh-CN"/>
+          </a:p>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="zh-CN" altLang="en-US"/>
+              <a:t>单位</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" altLang="zh-CN"/>
+              <a:t>:</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="zh-CN" altLang="en-US"/>
+              <a:t>百万美元</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" altLang="zh-CN"/>
+              <a:t>(</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="zh-CN" altLang="en-US"/>
+              <a:t>当期汇率</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" altLang="zh-CN"/>
+              <a:t>)</a:t>
+            </a:r>
+            <a:endParaRPr lang="zh-CN" altLang="en-US"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="zh-CN"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="stacked"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet!$A$115</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>英国</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:numFmt formatCode="0.00%" sourceLinked="0"/>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="zh-CN"/>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:layout/>
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet!$B$114:$F$114</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>欧洲</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>西海岸国家</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>拉丁美洲</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>亚洲</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>非洲</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet!$B$115:$F$115</c:f>
+              <c:numCache>
+                <c:formatCode>0.00%</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>8.3977982743231178E-2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.73874518929562338</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.43885578069129916</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.47098360655737703</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.50879073756432247</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet!$A$116</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>法国</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet!$B$114:$F$114</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>欧洲</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>西海岸国家</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>拉丁美洲</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>亚洲</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>非洲</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet!$B$116:$F$116</c:f>
+              <c:numCache>
+                <c:formatCode>0.00%</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0.39050877714965782</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3.4547570034905578E-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.13802145411203814</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.1360655737704918</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.21933962264150944</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet!$A$117</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>其他</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent3"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet!$B$114:$F$114</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>欧洲</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>西海岸国家</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>拉丁美洲</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>亚洲</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>非洲</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet!$B$117:$F$117</c:f>
+              <c:numCache>
+                <c:formatCode>0.00%</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0.25119012198750373</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>5.65649333213998E-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.11871275327771157</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.31360655737704918</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.16702401372212694</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet!$A$118</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>德国</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent4"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet!$B$114:$F$114</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>欧洲</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>西海岸国家</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>拉丁美洲</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>亚洲</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>非洲</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet!$B$118:$F$118</c:f>
+              <c:numCache>
+                <c:formatCode>0.00%</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0.22158583754834871</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>8.9501476774366776E-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.10786650774731824</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>3.9016393442622949E-2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.10205831903945112</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="4"/>
+          <c:order val="4"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet!$A$119</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>美国</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent5"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="zh-CN"/>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:layout/>
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet!$B$114:$F$114</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>欧洲</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>西海岸国家</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>拉丁美洲</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>亚洲</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>非洲</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet!$B$119:$F$119</c:f>
+              <c:numCache>
+                <c:formatCode>0.00%</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>5.2737280571258552E-2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>8.0551329096930094E-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.19654350417163291</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4.0327868852459016E-2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2.7873070325900515E-3</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="100"/>
+        <c:axId val="638337744"/>
+        <c:axId val="782224560"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="638337744"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="zh-CN"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="782224560"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="782224560"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0.00%" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="zh-CN"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="638337744"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="zh-CN"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="zh-CN"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:date1904 val="0"/>
+  <c:lang val="zh-CN"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="zh-CN" altLang="en-US"/>
+              <a:t>美国与主要国家的</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" altLang="zh-CN"/>
+              <a:t>GDP</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="zh-CN" altLang="en-US"/>
+              <a:t>总量比较</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" altLang="zh-CN"/>
+              <a:t>:19—20</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="zh-CN" altLang="en-US"/>
+              <a:t>世纪</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-US" altLang="zh-CN"/>
+          </a:p>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="zh-CN" altLang="en-US"/>
+              <a:t>单位</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" altLang="zh-CN"/>
+              <a:t>:</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="zh-CN" altLang="en-US"/>
+              <a:t>百万</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" altLang="zh-CN"/>
+              <a:t>/1990</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="zh-CN" altLang="en-US"/>
+              <a:t>国际元</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="zh-CN"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet!$A$140</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>美国</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet!$B$139:$G$139</c:f>
+              <c:strCache>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>1820年</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1870年</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1913年</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1950年</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1973年</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1998年</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet!$B$140:$G$140</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>12548</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>98374</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>517383</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1455916</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>3536622</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>7394598</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet!$A$141</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>中国</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet!$B$139:$G$139</c:f>
+              <c:strCache>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>1820年</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1870年</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1913年</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1950年</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1973年</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1998年</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet!$B$141:$G$141</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>228600</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>189740</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>241344</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>239903</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>740048</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>3873352</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet!$A$142</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>日本</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent3"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet!$B$139:$G$139</c:f>
+              <c:strCache>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>1820年</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1870年</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1913年</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1950年</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1973年</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1998年</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet!$B$142:$G$142</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>20739</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>25393</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>71653</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>160966</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1242932</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2581576</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet!$A$143</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>印度</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent4"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet!$B$139:$G$139</c:f>
+              <c:strCache>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>1820年</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1870年</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1913年</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1950年</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1973年</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1998年</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet!$B$143:$G$143</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>111417</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>134882</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>204241</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>222222</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>494832</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1702712</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="4"/>
+          <c:order val="4"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet!$A$144</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>德国</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent5"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent5"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent5"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet!$B$139:$G$139</c:f>
+              <c:strCache>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>1820年</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1870年</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1913年</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1950年</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1973年</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1998年</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet!$B$144:$G$144</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>26349</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>71429</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>237332</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>265354</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>944755</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1460069</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="5"/>
+          <c:order val="5"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet!$A$145</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>法国</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent6"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent6"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent6"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet!$B$139:$G$139</c:f>
+              <c:strCache>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>1820年</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1870年</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1913年</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1950年</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1973年</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1998年</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet!$B$145:$G$145</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>38434</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>72100</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>144489</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>220492</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>683965</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1150080</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="6"/>
+          <c:order val="6"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet!$A$146</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>前苏联</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1">
+                    <a:lumMod val="60000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet!$B$139:$G$139</c:f>
+              <c:strCache>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>1820年</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1870年</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1913年</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1950年</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1973年</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1998年</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet!$B$146:$G$146</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>37710</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>83646</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>232351</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>510243</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1513070</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1132434</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="7"/>
+          <c:order val="7"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet!$A$147</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>英国</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent2">
+                    <a:lumMod val="60000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet!$B$139:$G$139</c:f>
+              <c:strCache>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>1820年</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1870年</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1913年</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1950年</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1973年</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1998年</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet!$B$147:$G$147</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>36232</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>100179</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>224618</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>347850</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>675941</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1108568</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:marker val="1"/>
+        <c:smooth val="0"/>
+        <c:axId val="8476344"/>
+        <c:axId val="8475168"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="8476344"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="zh-CN"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="8475168"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="8475168"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="zh-CN"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="8476344"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2192,7 +5091,1636 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="332">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="332">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="332">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="332">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -2722,6 +7250,96 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>523874</xdr:colOff>
+      <xdr:row>52</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>609599</xdr:colOff>
+      <xdr:row>100</xdr:row>
+      <xdr:rowOff>9524</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name="图表 3"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>247650</xdr:colOff>
+      <xdr:row>112</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>514350</xdr:colOff>
+      <xdr:row>135</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="5" name="图表 4"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>119061</xdr:colOff>
+      <xdr:row>138</xdr:row>
+      <xdr:rowOff>4762</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>638174</xdr:colOff>
+      <xdr:row>152</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="7" name="图表 6"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2993,11 +7611,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:P10"/>
+  <dimension ref="A1:P161"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="7.625" bestFit="1" customWidth="1"/>
-    <col min="2" max="6" width="6.875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.25" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="8.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="21" customHeight="1">
@@ -3024,19 +7645,19 @@
       <c r="A2" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="20">
+      <c r="B2" s="19">
         <v>73.3</v>
       </c>
-      <c r="C2" s="21">
+      <c r="C2" s="20">
         <v>100</v>
       </c>
-      <c r="D2" s="22">
+      <c r="D2" s="21">
         <v>127.2</v>
       </c>
-      <c r="E2" s="23">
+      <c r="E2" s="22">
         <v>135</v>
       </c>
-      <c r="F2" s="24">
+      <c r="F2" s="23">
         <v>181</v>
       </c>
     </row>
@@ -3044,19 +7665,19 @@
       <c r="A3" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="25">
+      <c r="B3" s="24">
         <v>46.9</v>
       </c>
-      <c r="C3" s="26">
+      <c r="C3" s="25">
         <v>127.8</v>
       </c>
-      <c r="D3" s="27">
+      <c r="D3" s="26">
         <v>298.10000000000002</v>
       </c>
-      <c r="E3" s="28">
+      <c r="E3" s="27">
         <v>533</v>
       </c>
-      <c r="F3" s="29">
+      <c r="F3" s="28">
         <v>528</v>
       </c>
       <c r="H3" s="1" t="s">
@@ -3091,46 +7712,46 @@
       <c r="A4" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="30">
+      <c r="B4" s="29">
         <v>27.4</v>
       </c>
-      <c r="C4" s="31">
+      <c r="C4" s="30">
         <v>71.2</v>
       </c>
-      <c r="D4" s="32">
+      <c r="D4" s="31">
         <v>137.69999999999999</v>
       </c>
-      <c r="E4" s="33">
+      <c r="E4" s="32">
         <v>158</v>
       </c>
-      <c r="F4" s="34">
+      <c r="F4" s="33">
         <v>214</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="I4" s="20">
+      <c r="I4" s="19">
         <v>73.3</v>
       </c>
-      <c r="J4" s="25">
+      <c r="J4" s="24">
         <v>46.9</v>
       </c>
-      <c r="K4" s="30">
+      <c r="K4" s="29">
         <v>27.4</v>
       </c>
-      <c r="L4" s="35">
+      <c r="L4" s="34">
         <v>25.1</v>
       </c>
-      <c r="M4" s="40">
+      <c r="M4" s="39">
         <v>24.5</v>
       </c>
-      <c r="N4" s="45">
+      <c r="N4" s="44">
         <v>14</v>
       </c>
-      <c r="O4" s="48">
+      <c r="O4" s="47">
         <v>8.1</v>
       </c>
-      <c r="P4" s="52">
+      <c r="P4" s="51">
         <v>7.6</v>
       </c>
     </row>
@@ -3138,46 +7759,46 @@
       <c r="A5" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="35">
+      <c r="B5" s="34">
         <v>25.1</v>
       </c>
-      <c r="C5" s="36">
+      <c r="C5" s="35">
         <v>36.799999999999997</v>
       </c>
-      <c r="D5" s="37">
+      <c r="D5" s="36">
         <v>57.3</v>
       </c>
-      <c r="E5" s="38">
+      <c r="E5" s="37">
         <v>82</v>
       </c>
-      <c r="F5" s="39">
+      <c r="F5" s="38">
         <v>74</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="I5" s="21">
+      <c r="I5" s="20">
         <v>100</v>
       </c>
-      <c r="J5" s="26">
+      <c r="J5" s="25">
         <v>127.8</v>
       </c>
-      <c r="K5" s="31">
+      <c r="K5" s="30">
         <v>71.2</v>
       </c>
-      <c r="L5" s="36">
+      <c r="L5" s="35">
         <v>36.799999999999997</v>
       </c>
-      <c r="M5" s="41">
+      <c r="M5" s="40">
         <v>47.5</v>
       </c>
-      <c r="N5" s="46">
+      <c r="N5" s="45">
         <v>25.6</v>
       </c>
-      <c r="O5" s="49">
+      <c r="O5" s="48">
         <v>13.6</v>
       </c>
-      <c r="P5" s="53">
+      <c r="P5" s="52">
         <v>13</v>
       </c>
     </row>
@@ -3185,43 +7806,43 @@
       <c r="A6" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="40">
+      <c r="B6" s="39">
         <v>24.5</v>
       </c>
-      <c r="C6" s="41">
+      <c r="C6" s="40">
         <v>47.5</v>
       </c>
-      <c r="D6" s="42">
+      <c r="D6" s="41">
         <v>76.599999999999994</v>
       </c>
-      <c r="E6" s="43">
+      <c r="E6" s="42">
         <v>72</v>
       </c>
-      <c r="F6" s="44">
+      <c r="F6" s="43">
         <v>152</v>
       </c>
       <c r="H6" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="22">
+      <c r="I6" s="21">
         <v>127.2</v>
       </c>
-      <c r="J6" s="27">
+      <c r="J6" s="26">
         <v>298.10000000000002</v>
       </c>
-      <c r="K6" s="32">
+      <c r="K6" s="31">
         <v>137.69999999999999</v>
       </c>
-      <c r="L6" s="37">
+      <c r="L6" s="36">
         <v>57.3</v>
       </c>
-      <c r="M6" s="42">
+      <c r="M6" s="41">
         <v>76.599999999999994</v>
       </c>
-      <c r="N6" s="47">
+      <c r="N6" s="46">
         <v>40.700000000000003</v>
       </c>
-      <c r="O6" s="50">
+      <c r="O6" s="49">
         <v>22.5</v>
       </c>
       <c r="P6" s="18">
@@ -3232,13 +7853,13 @@
       <c r="A7" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="45">
+      <c r="B7" s="44">
         <v>14</v>
       </c>
-      <c r="C7" s="46">
+      <c r="C7" s="45">
         <v>25.6</v>
       </c>
-      <c r="D7" s="47">
+      <c r="D7" s="46">
         <v>40.700000000000003</v>
       </c>
       <c r="E7" s="13"/>
@@ -3246,26 +7867,26 @@
       <c r="H7" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="I7" s="23">
+      <c r="I7" s="22">
         <v>135</v>
       </c>
-      <c r="J7" s="28">
+      <c r="J7" s="27">
         <v>533</v>
       </c>
-      <c r="K7" s="33">
+      <c r="K7" s="32">
         <v>158</v>
       </c>
-      <c r="L7" s="38">
+      <c r="L7" s="37">
         <v>82</v>
       </c>
-      <c r="M7" s="43">
+      <c r="M7" s="42">
         <v>72</v>
       </c>
       <c r="N7" s="13"/>
       <c r="O7" s="16">
         <v>37</v>
       </c>
-      <c r="P7" s="54">
+      <c r="P7" s="53">
         <v>45</v>
       </c>
     </row>
@@ -3273,44 +7894,44 @@
       <c r="A8" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="48">
+      <c r="B8" s="47">
         <v>8.1</v>
       </c>
-      <c r="C8" s="49">
+      <c r="C8" s="48">
         <v>13.6</v>
       </c>
-      <c r="D8" s="50">
+      <c r="D8" s="49">
         <v>22.5</v>
       </c>
       <c r="E8" s="16">
         <v>37</v>
       </c>
-      <c r="F8" s="51">
+      <c r="F8" s="50">
         <v>46</v>
       </c>
       <c r="H8" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="I8" s="24">
+      <c r="I8" s="23">
         <v>181</v>
       </c>
-      <c r="J8" s="29">
+      <c r="J8" s="28">
         <v>528</v>
       </c>
-      <c r="K8" s="34">
+      <c r="K8" s="33">
         <v>214</v>
       </c>
-      <c r="L8" s="39">
+      <c r="L8" s="38">
         <v>74</v>
       </c>
-      <c r="M8" s="44">
+      <c r="M8" s="43">
         <v>152</v>
       </c>
       <c r="N8" s="14"/>
-      <c r="O8" s="51">
+      <c r="O8" s="50">
         <v>46</v>
       </c>
-      <c r="P8" s="55">
+      <c r="P8" s="54">
         <v>88</v>
       </c>
     </row>
@@ -3318,37 +7939,1094 @@
       <c r="A9" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="B9" s="52">
+      <c r="B9" s="51">
         <v>7.6</v>
       </c>
-      <c r="C9" s="53">
+      <c r="C9" s="52">
         <v>13</v>
       </c>
       <c r="D9" s="18">
         <v>25.1</v>
       </c>
-      <c r="E9" s="54">
+      <c r="E9" s="53">
         <v>45</v>
       </c>
-      <c r="F9" s="55">
+      <c r="F9" s="54">
         <v>88</v>
       </c>
     </row>
     <row r="10" spans="1:16">
-      <c r="A10" s="19"/>
-      <c r="B10" s="19"/>
-      <c r="C10" s="19"/>
-      <c r="D10" s="19"/>
-      <c r="E10" s="19"/>
-      <c r="F10" s="19"/>
+      <c r="A10" s="55"/>
+      <c r="B10" s="55"/>
+      <c r="C10" s="55"/>
+      <c r="D10" s="55"/>
+      <c r="E10" s="55"/>
+      <c r="F10" s="55"/>
+    </row>
+    <row r="52" spans="1:7" ht="14.25" thickBot="1"/>
+    <row r="53" spans="1:7" ht="14.25" thickTop="1">
+      <c r="A53" s="58" t="s">
+        <v>17</v>
+      </c>
+      <c r="B53" s="56" t="s">
+        <v>15</v>
+      </c>
+      <c r="C53" s="56">
+        <v>1600</v>
+      </c>
+      <c r="D53" s="56">
+        <v>1700</v>
+      </c>
+      <c r="E53" s="56">
+        <v>1820</v>
+      </c>
+      <c r="F53" s="56">
+        <v>1870</v>
+      </c>
+      <c r="G53" s="61" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7">
+      <c r="A54" s="59" t="s">
+        <v>7</v>
+      </c>
+      <c r="B54" s="62">
+        <v>800</v>
+      </c>
+      <c r="C54" s="62">
+        <v>600</v>
+      </c>
+      <c r="D54" s="62">
+        <v>527</v>
+      </c>
+      <c r="E54" s="62">
+        <v>12548</v>
+      </c>
+      <c r="F54" s="62">
+        <v>98374</v>
+      </c>
+      <c r="G54" s="63">
+        <v>517383</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7">
+      <c r="A55" s="59" t="s">
+        <v>8</v>
+      </c>
+      <c r="B55" s="62">
+        <v>8112</v>
+      </c>
+      <c r="C55" s="62">
+        <v>12432</v>
+      </c>
+      <c r="D55" s="62">
+        <v>13410</v>
+      </c>
+      <c r="E55" s="62">
+        <v>26349</v>
+      </c>
+      <c r="F55" s="62">
+        <v>71429</v>
+      </c>
+      <c r="G55" s="63">
+        <v>237332</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7">
+      <c r="A56" s="59" t="s">
+        <v>14</v>
+      </c>
+      <c r="B56" s="62">
+        <v>8475</v>
+      </c>
+      <c r="C56" s="62">
+        <v>11447</v>
+      </c>
+      <c r="D56" s="62">
+        <v>16222</v>
+      </c>
+      <c r="E56" s="62">
+        <v>37710</v>
+      </c>
+      <c r="F56" s="62">
+        <v>83646</v>
+      </c>
+      <c r="G56" s="63">
+        <v>232351</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7">
+      <c r="A57" s="66" t="s">
+        <v>6</v>
+      </c>
+      <c r="B57" s="67">
+        <v>2815</v>
+      </c>
+      <c r="C57" s="67">
+        <v>6007</v>
+      </c>
+      <c r="D57" s="67">
+        <v>10709</v>
+      </c>
+      <c r="E57" s="67">
+        <v>36232</v>
+      </c>
+      <c r="F57" s="67">
+        <v>100719</v>
+      </c>
+      <c r="G57" s="68">
+        <v>224618</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" ht="24.75" thickBot="1">
+      <c r="A58" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="B58" s="64">
+        <v>10912</v>
+      </c>
+      <c r="C58" s="64">
+        <v>15559</v>
+      </c>
+      <c r="D58" s="64">
+        <v>21180</v>
+      </c>
+      <c r="E58" s="64">
+        <v>38434</v>
+      </c>
+      <c r="F58" s="64">
+        <v>72100</v>
+      </c>
+      <c r="G58" s="65">
+        <v>144489</v>
+      </c>
+    </row>
+    <row r="102" spans="1:7">
+      <c r="A102" s="57" t="s">
+        <v>0</v>
+      </c>
+      <c r="B102" s="57" t="s">
+        <v>18</v>
+      </c>
+      <c r="C102" s="57" t="s">
+        <v>19</v>
+      </c>
+      <c r="D102" s="57" t="s">
+        <v>20</v>
+      </c>
+      <c r="E102" s="57" t="s">
+        <v>21</v>
+      </c>
+      <c r="F102" s="57" t="s">
+        <v>22</v>
+      </c>
+      <c r="G102" s="57" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="103" spans="1:7">
+      <c r="A103" s="57" t="s">
+        <v>6</v>
+      </c>
+      <c r="B103" s="57">
+        <v>1129</v>
+      </c>
+      <c r="C103" s="57">
+        <v>8254</v>
+      </c>
+      <c r="D103" s="57">
+        <v>3682</v>
+      </c>
+      <c r="E103" s="57">
+        <v>2873</v>
+      </c>
+      <c r="F103" s="57">
+        <v>2373</v>
+      </c>
+      <c r="G103" s="57">
+        <v>18311</v>
+      </c>
+    </row>
+    <row r="104" spans="1:7">
+      <c r="A104" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="B104" s="57">
+        <v>5250</v>
+      </c>
+      <c r="C104" s="57">
+        <v>386</v>
+      </c>
+      <c r="D104" s="57">
+        <v>1158</v>
+      </c>
+      <c r="E104" s="57">
+        <v>830</v>
+      </c>
+      <c r="F104" s="57">
+        <v>1023</v>
+      </c>
+      <c r="G104" s="57">
+        <v>8647</v>
+      </c>
+    </row>
+    <row r="105" spans="1:7">
+      <c r="A105" s="57" t="s">
+        <v>24</v>
+      </c>
+      <c r="B105" s="57">
+        <v>3377</v>
+      </c>
+      <c r="C105" s="57">
+        <v>632</v>
+      </c>
+      <c r="D105" s="57">
+        <v>996</v>
+      </c>
+      <c r="E105" s="57">
+        <v>1913</v>
+      </c>
+      <c r="F105" s="57">
+        <v>779</v>
+      </c>
+      <c r="G105" s="57">
+        <v>7700</v>
+      </c>
+    </row>
+    <row r="106" spans="1:7">
+      <c r="A106" s="57" t="s">
+        <v>8</v>
+      </c>
+      <c r="B106" s="57">
+        <v>2979</v>
+      </c>
+      <c r="C106" s="57">
+        <v>1000</v>
+      </c>
+      <c r="D106" s="57">
+        <v>905</v>
+      </c>
+      <c r="E106" s="57">
+        <v>238</v>
+      </c>
+      <c r="F106" s="57">
+        <v>476</v>
+      </c>
+      <c r="G106" s="57">
+        <v>5598</v>
+      </c>
+    </row>
+    <row r="107" spans="1:7">
+      <c r="A107" s="57" t="s">
+        <v>7</v>
+      </c>
+      <c r="B107" s="57">
+        <v>709</v>
+      </c>
+      <c r="C107" s="57">
+        <v>900</v>
+      </c>
+      <c r="D107" s="57">
+        <v>1649</v>
+      </c>
+      <c r="E107" s="57">
+        <v>246</v>
+      </c>
+      <c r="F107" s="57">
+        <v>13</v>
+      </c>
+      <c r="G107" s="57">
+        <v>3514</v>
+      </c>
+    </row>
+    <row r="108" spans="1:7">
+      <c r="A108" s="57" t="s">
+        <v>23</v>
+      </c>
+      <c r="B108" s="57">
+        <v>13444</v>
+      </c>
+      <c r="C108" s="57">
+        <v>11173</v>
+      </c>
+      <c r="D108" s="57">
+        <v>8390</v>
+      </c>
+      <c r="E108" s="57">
+        <v>6100</v>
+      </c>
+      <c r="F108" s="57">
+        <v>4664</v>
+      </c>
+      <c r="G108" s="57">
+        <v>43770</v>
+      </c>
+    </row>
+    <row r="113" spans="1:7">
+      <c r="A113" s="57"/>
+      <c r="B113" s="57"/>
+      <c r="C113" s="57"/>
+      <c r="D113" s="57"/>
+      <c r="E113" s="57"/>
+      <c r="F113" s="57"/>
+      <c r="G113" s="57"/>
+    </row>
+    <row r="114" spans="1:7">
+      <c r="A114" s="57" t="s">
+        <v>0</v>
+      </c>
+      <c r="B114" s="57" t="s">
+        <v>18</v>
+      </c>
+      <c r="C114" s="57" t="s">
+        <v>26</v>
+      </c>
+      <c r="D114" s="57" t="s">
+        <v>20</v>
+      </c>
+      <c r="E114" s="57" t="s">
+        <v>21</v>
+      </c>
+      <c r="F114" s="57" t="s">
+        <v>22</v>
+      </c>
+      <c r="G114" s="57" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="115" spans="1:7">
+      <c r="A115" s="57" t="s">
+        <v>6</v>
+      </c>
+      <c r="B115" s="69">
+        <f>B103/B$108</f>
+        <v>8.3977982743231178E-2</v>
+      </c>
+      <c r="C115" s="69">
+        <f t="shared" ref="C115:F115" si="0">C103/C$108</f>
+        <v>0.73874518929562338</v>
+      </c>
+      <c r="D115" s="69">
+        <f t="shared" si="0"/>
+        <v>0.43885578069129916</v>
+      </c>
+      <c r="E115" s="69">
+        <f t="shared" si="0"/>
+        <v>0.47098360655737703</v>
+      </c>
+      <c r="F115" s="69">
+        <f t="shared" si="0"/>
+        <v>0.50879073756432247</v>
+      </c>
+      <c r="G115" s="57">
+        <v>18311</v>
+      </c>
+    </row>
+    <row r="116" spans="1:7">
+      <c r="A116" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="B116" s="69">
+        <f t="shared" ref="B116:F116" si="1">B104/B$108</f>
+        <v>0.39050877714965782</v>
+      </c>
+      <c r="C116" s="69">
+        <f t="shared" si="1"/>
+        <v>3.4547570034905578E-2</v>
+      </c>
+      <c r="D116" s="69">
+        <f t="shared" si="1"/>
+        <v>0.13802145411203814</v>
+      </c>
+      <c r="E116" s="69">
+        <f t="shared" si="1"/>
+        <v>0.1360655737704918</v>
+      </c>
+      <c r="F116" s="69">
+        <f t="shared" si="1"/>
+        <v>0.21933962264150944</v>
+      </c>
+      <c r="G116" s="57">
+        <v>8647</v>
+      </c>
+    </row>
+    <row r="117" spans="1:7">
+      <c r="A117" s="57" t="s">
+        <v>24</v>
+      </c>
+      <c r="B117" s="69">
+        <f t="shared" ref="B117:F117" si="2">B105/B$108</f>
+        <v>0.25119012198750373</v>
+      </c>
+      <c r="C117" s="69">
+        <f t="shared" si="2"/>
+        <v>5.65649333213998E-2</v>
+      </c>
+      <c r="D117" s="69">
+        <f t="shared" si="2"/>
+        <v>0.11871275327771157</v>
+      </c>
+      <c r="E117" s="69">
+        <f t="shared" si="2"/>
+        <v>0.31360655737704918</v>
+      </c>
+      <c r="F117" s="69">
+        <f t="shared" si="2"/>
+        <v>0.16702401372212694</v>
+      </c>
+      <c r="G117" s="57">
+        <v>7700</v>
+      </c>
+    </row>
+    <row r="118" spans="1:7">
+      <c r="A118" s="57" t="s">
+        <v>8</v>
+      </c>
+      <c r="B118" s="69">
+        <f t="shared" ref="B118:F118" si="3">B106/B$108</f>
+        <v>0.22158583754834871</v>
+      </c>
+      <c r="C118" s="69">
+        <f t="shared" si="3"/>
+        <v>8.9501476774366776E-2</v>
+      </c>
+      <c r="D118" s="69">
+        <f t="shared" si="3"/>
+        <v>0.10786650774731824</v>
+      </c>
+      <c r="E118" s="69">
+        <f t="shared" si="3"/>
+        <v>3.9016393442622949E-2</v>
+      </c>
+      <c r="F118" s="69">
+        <f t="shared" si="3"/>
+        <v>0.10205831903945112</v>
+      </c>
+      <c r="G118" s="57">
+        <v>5598</v>
+      </c>
+    </row>
+    <row r="119" spans="1:7">
+      <c r="A119" s="57" t="s">
+        <v>7</v>
+      </c>
+      <c r="B119" s="69">
+        <f t="shared" ref="B119:F119" si="4">B107/B$108</f>
+        <v>5.2737280571258552E-2</v>
+      </c>
+      <c r="C119" s="69">
+        <f t="shared" si="4"/>
+        <v>8.0551329096930094E-2</v>
+      </c>
+      <c r="D119" s="69">
+        <f t="shared" si="4"/>
+        <v>0.19654350417163291</v>
+      </c>
+      <c r="E119" s="69">
+        <f t="shared" si="4"/>
+        <v>4.0327868852459016E-2</v>
+      </c>
+      <c r="F119" s="69">
+        <f t="shared" si="4"/>
+        <v>2.7873070325900515E-3</v>
+      </c>
+      <c r="G119" s="57">
+        <v>3514</v>
+      </c>
+    </row>
+    <row r="120" spans="1:7">
+      <c r="A120" t="s">
+        <v>25</v>
+      </c>
+      <c r="B120" s="69">
+        <f>SUM(B115:B119)</f>
+        <v>1</v>
+      </c>
+      <c r="C120" s="69">
+        <f t="shared" ref="C120:F120" si="5">SUM(C115:C119)</f>
+        <v>0.99991049852322567</v>
+      </c>
+      <c r="D120" s="69">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="E120" s="69">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="F120" s="69">
+        <f t="shared" si="5"/>
+        <v>0.99999999999999989</v>
+      </c>
+    </row>
+    <row r="122" spans="1:7">
+      <c r="C122" s="57"/>
+      <c r="D122" s="57"/>
+    </row>
+    <row r="123" spans="1:7">
+      <c r="B123" s="57"/>
+      <c r="C123" s="57"/>
+      <c r="D123" s="57"/>
+    </row>
+    <row r="124" spans="1:7">
+      <c r="B124" s="57"/>
+      <c r="C124" s="57"/>
+      <c r="D124" s="57"/>
+    </row>
+    <row r="139" spans="1:7">
+      <c r="A139" s="57" t="s">
+        <v>0</v>
+      </c>
+      <c r="B139" s="57" t="s">
+        <v>27</v>
+      </c>
+      <c r="C139" s="57" t="s">
+        <v>28</v>
+      </c>
+      <c r="D139" s="57" t="s">
+        <v>3</v>
+      </c>
+      <c r="E139" s="57" t="s">
+        <v>29</v>
+      </c>
+      <c r="F139" s="57" t="s">
+        <v>30</v>
+      </c>
+      <c r="G139" s="57" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="140" spans="1:7">
+      <c r="A140" s="57" t="s">
+        <v>7</v>
+      </c>
+      <c r="B140" s="57">
+        <v>12548</v>
+      </c>
+      <c r="C140" s="57">
+        <v>98374</v>
+      </c>
+      <c r="D140" s="57">
+        <v>517383</v>
+      </c>
+      <c r="E140" s="57">
+        <v>1455916</v>
+      </c>
+      <c r="F140" s="57">
+        <v>3536622</v>
+      </c>
+      <c r="G140" s="57">
+        <v>7394598</v>
+      </c>
+    </row>
+    <row r="141" spans="1:7">
+      <c r="A141" s="57" t="s">
+        <v>33</v>
+      </c>
+      <c r="B141" s="57">
+        <v>228600</v>
+      </c>
+      <c r="C141" s="57">
+        <v>189740</v>
+      </c>
+      <c r="D141" s="57">
+        <v>241344</v>
+      </c>
+      <c r="E141" s="57">
+        <v>239903</v>
+      </c>
+      <c r="F141" s="57">
+        <v>740048</v>
+      </c>
+      <c r="G141" s="57">
+        <v>3873352</v>
+      </c>
+    </row>
+    <row r="142" spans="1:7">
+      <c r="A142" s="57" t="s">
+        <v>13</v>
+      </c>
+      <c r="B142" s="57">
+        <v>20739</v>
+      </c>
+      <c r="C142" s="57">
+        <v>25393</v>
+      </c>
+      <c r="D142" s="57">
+        <v>71653</v>
+      </c>
+      <c r="E142" s="57">
+        <v>160966</v>
+      </c>
+      <c r="F142" s="57">
+        <v>1242932</v>
+      </c>
+      <c r="G142" s="57">
+        <v>2581576</v>
+      </c>
+    </row>
+    <row r="143" spans="1:7">
+      <c r="A143" s="57" t="s">
+        <v>34</v>
+      </c>
+      <c r="B143" s="57">
+        <v>111417</v>
+      </c>
+      <c r="C143" s="57">
+        <v>134882</v>
+      </c>
+      <c r="D143" s="57">
+        <v>204241</v>
+      </c>
+      <c r="E143" s="57">
+        <v>222222</v>
+      </c>
+      <c r="F143" s="57">
+        <v>494832</v>
+      </c>
+      <c r="G143" s="57">
+        <v>1702712</v>
+      </c>
+    </row>
+    <row r="144" spans="1:7">
+      <c r="A144" s="57" t="s">
+        <v>8</v>
+      </c>
+      <c r="B144" s="57">
+        <v>26349</v>
+      </c>
+      <c r="C144" s="57">
+        <v>71429</v>
+      </c>
+      <c r="D144" s="57">
+        <v>237332</v>
+      </c>
+      <c r="E144" s="57">
+        <v>265354</v>
+      </c>
+      <c r="F144" s="57">
+        <v>944755</v>
+      </c>
+      <c r="G144" s="57">
+        <v>1460069</v>
+      </c>
+    </row>
+    <row r="145" spans="1:7">
+      <c r="A145" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="B145" s="57">
+        <v>38434</v>
+      </c>
+      <c r="C145" s="57">
+        <v>72100</v>
+      </c>
+      <c r="D145" s="57">
+        <v>144489</v>
+      </c>
+      <c r="E145" s="57">
+        <v>220492</v>
+      </c>
+      <c r="F145" s="57">
+        <v>683965</v>
+      </c>
+      <c r="G145" s="57">
+        <v>1150080</v>
+      </c>
+    </row>
+    <row r="146" spans="1:7">
+      <c r="A146" s="57" t="s">
+        <v>32</v>
+      </c>
+      <c r="B146" s="57">
+        <v>37710</v>
+      </c>
+      <c r="C146" s="57">
+        <v>83646</v>
+      </c>
+      <c r="D146" s="57">
+        <v>232351</v>
+      </c>
+      <c r="E146" s="57">
+        <v>510243</v>
+      </c>
+      <c r="F146" s="57">
+        <v>1513070</v>
+      </c>
+      <c r="G146" s="57">
+        <v>1132434</v>
+      </c>
+    </row>
+    <row r="147" spans="1:7">
+      <c r="A147" s="57" t="s">
+        <v>6</v>
+      </c>
+      <c r="B147" s="57">
+        <v>36232</v>
+      </c>
+      <c r="C147" s="57">
+        <v>100179</v>
+      </c>
+      <c r="D147" s="57">
+        <v>224618</v>
+      </c>
+      <c r="E147" s="57">
+        <v>347850</v>
+      </c>
+      <c r="F147" s="57">
+        <v>675941</v>
+      </c>
+      <c r="G147" s="57">
+        <v>1108568</v>
+      </c>
+    </row>
+    <row r="153" spans="1:7">
+      <c r="A153" s="57" t="s">
+        <v>0</v>
+      </c>
+      <c r="B153" s="57" t="s">
+        <v>27</v>
+      </c>
+      <c r="C153" s="57" t="s">
+        <v>28</v>
+      </c>
+      <c r="D153" s="57" t="s">
+        <v>3</v>
+      </c>
+      <c r="E153" s="57" t="s">
+        <v>29</v>
+      </c>
+      <c r="F153" s="57" t="s">
+        <v>30</v>
+      </c>
+      <c r="G153" s="57" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="154" spans="1:7">
+      <c r="A154" s="57" t="s">
+        <v>7</v>
+      </c>
+      <c r="B154" s="69">
+        <f>B140/B$140</f>
+        <v>1</v>
+      </c>
+      <c r="C154" s="69">
+        <f t="shared" ref="C154:G154" si="6">C140/C$140</f>
+        <v>1</v>
+      </c>
+      <c r="D154" s="69">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="E154" s="69">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="F154" s="69">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="G154" s="69">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="155" spans="1:7">
+      <c r="A155" s="57" t="s">
+        <v>33</v>
+      </c>
+      <c r="B155" s="69">
+        <f t="shared" ref="B155:G161" si="7">B141/B$140</f>
+        <v>18.218042715970672</v>
+      </c>
+      <c r="C155" s="69">
+        <f t="shared" si="7"/>
+        <v>1.9287616646674934</v>
+      </c>
+      <c r="D155" s="69">
+        <f t="shared" si="7"/>
+        <v>0.46647068032772626</v>
+      </c>
+      <c r="E155" s="69">
+        <f t="shared" si="7"/>
+        <v>0.16477805038202753</v>
+      </c>
+      <c r="F155" s="69">
+        <f t="shared" si="7"/>
+        <v>0.20925278415391863</v>
+      </c>
+      <c r="G155" s="69">
+        <f t="shared" si="7"/>
+        <v>0.52380832602394345</v>
+      </c>
+    </row>
+    <row r="156" spans="1:7">
+      <c r="A156" s="57" t="s">
+        <v>13</v>
+      </c>
+      <c r="B156" s="69">
+        <f t="shared" si="7"/>
+        <v>1.6527733503347146</v>
+      </c>
+      <c r="C156" s="69">
+        <f t="shared" si="7"/>
+        <v>0.25812714741700044</v>
+      </c>
+      <c r="D156" s="69">
+        <f t="shared" si="7"/>
+        <v>0.13849121443881998</v>
+      </c>
+      <c r="E156" s="69">
+        <f t="shared" si="7"/>
+        <v>0.11055994988721876</v>
+      </c>
+      <c r="F156" s="69">
+        <f t="shared" si="7"/>
+        <v>0.35144609743421829</v>
+      </c>
+      <c r="G156" s="69">
+        <f t="shared" si="7"/>
+        <v>0.34911647664957579</v>
+      </c>
+    </row>
+    <row r="157" spans="1:7">
+      <c r="A157" s="57" t="s">
+        <v>34</v>
+      </c>
+      <c r="B157" s="69">
+        <f t="shared" si="7"/>
+        <v>8.879263627669749</v>
+      </c>
+      <c r="C157" s="69">
+        <f t="shared" si="7"/>
+        <v>1.3711143188240795</v>
+      </c>
+      <c r="D157" s="69">
+        <f t="shared" si="7"/>
+        <v>0.39475784863437724</v>
+      </c>
+      <c r="E157" s="69">
+        <f t="shared" si="7"/>
+        <v>0.15263380579648825</v>
+      </c>
+      <c r="F157" s="69">
+        <f t="shared" si="7"/>
+        <v>0.13991656445048412</v>
+      </c>
+      <c r="G157" s="69">
+        <f t="shared" si="7"/>
+        <v>0.23026430916190441</v>
+      </c>
+    </row>
+    <row r="158" spans="1:7">
+      <c r="A158" s="57" t="s">
+        <v>8</v>
+      </c>
+      <c r="B158" s="69">
+        <f t="shared" si="7"/>
+        <v>2.099856550844756</v>
+      </c>
+      <c r="C158" s="69">
+        <f t="shared" si="7"/>
+        <v>0.72609632626507004</v>
+      </c>
+      <c r="D158" s="69">
+        <f t="shared" si="7"/>
+        <v>0.45871627015189909</v>
+      </c>
+      <c r="E158" s="69">
+        <f t="shared" si="7"/>
+        <v>0.18225914132408738</v>
+      </c>
+      <c r="F158" s="69">
+        <f t="shared" si="7"/>
+        <v>0.26713485354103433</v>
+      </c>
+      <c r="G158" s="69">
+        <f t="shared" si="7"/>
+        <v>0.19745076067691578</v>
+      </c>
+    </row>
+    <row r="159" spans="1:7">
+      <c r="A159" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="B159" s="69">
+        <f t="shared" si="7"/>
+        <v>3.062958240357029</v>
+      </c>
+      <c r="C159" s="69">
+        <f t="shared" si="7"/>
+        <v>0.73291723422855637</v>
+      </c>
+      <c r="D159" s="69">
+        <f t="shared" si="7"/>
+        <v>0.27926893616527793</v>
+      </c>
+      <c r="E159" s="69">
+        <f t="shared" si="7"/>
+        <v>0.15144555043010724</v>
+      </c>
+      <c r="F159" s="69">
+        <f t="shared" si="7"/>
+        <v>0.19339499669458596</v>
+      </c>
+      <c r="G159" s="69">
+        <f t="shared" si="7"/>
+        <v>0.15552975293585938</v>
+      </c>
+    </row>
+    <row r="160" spans="1:7">
+      <c r="A160" s="57" t="s">
+        <v>32</v>
+      </c>
+      <c r="B160" s="69">
+        <f t="shared" si="7"/>
+        <v>3.0052598023589416</v>
+      </c>
+      <c r="C160" s="69">
+        <f t="shared" si="7"/>
+        <v>0.85028564458088518</v>
+      </c>
+      <c r="D160" s="69">
+        <f t="shared" si="7"/>
+        <v>0.44908897277258819</v>
+      </c>
+      <c r="E160" s="69">
+        <f t="shared" si="7"/>
+        <v>0.35046183983141882</v>
+      </c>
+      <c r="F160" s="69">
+        <f t="shared" si="7"/>
+        <v>0.42782915448696524</v>
+      </c>
+      <c r="G160" s="69">
+        <f t="shared" si="7"/>
+        <v>0.15314341631553197</v>
+      </c>
+    </row>
+    <row r="161" spans="1:7">
+      <c r="A161" s="57" t="s">
+        <v>6</v>
+      </c>
+      <c r="B161" s="69">
+        <f t="shared" si="7"/>
+        <v>2.8874721071087026</v>
+      </c>
+      <c r="C161" s="69">
+        <f t="shared" si="7"/>
+        <v>1.0183483440746539</v>
+      </c>
+      <c r="D161" s="69">
+        <f t="shared" si="7"/>
+        <v>0.4341425984232184</v>
+      </c>
+      <c r="E161" s="69">
+        <f t="shared" si="7"/>
+        <v>0.23892175098013896</v>
+      </c>
+      <c r="F161" s="69">
+        <f t="shared" si="7"/>
+        <v>0.19112616502413884</v>
+      </c>
+      <c r="G161" s="69">
+        <f t="shared" si="7"/>
+        <v>0.14991592511181812</v>
+      </c>
     </row>
   </sheetData>
+  <sortState ref="A140:G147">
+    <sortCondition descending="1" ref="G140:G147"/>
+  </sortState>
   <mergeCells count="1">
     <mergeCell ref="A10:F10"/>
   </mergeCells>
   <phoneticPr fontId="53" type="noConversion"/>
+  <conditionalFormatting sqref="B54:G58">
+    <cfRule type="dataBar" priority="3">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{1ECC34C0-F07B-48AE-9C77-1BCAC518A26B}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B103:G108">
+    <cfRule type="dataBar" priority="4">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{A7BC987F-1766-4FA0-84EF-001CBF13BBBF}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B115:G119">
+    <cfRule type="dataBar" priority="1">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{C4A2DCA3-CD44-4809-824F-F947229E48E5}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
   <drawing r:id="rId2"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
+      <x14:conditionalFormattings>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{1ECC34C0-F07B-48AE-9C77-1BCAC518A26B}">
+            <x14:dataBar minLength="0" maxLength="100" gradient="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>B54:G58</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{A7BC987F-1766-4FA0-84EF-001CBF13BBBF}">
+            <x14:dataBar minLength="0" maxLength="100" gradient="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>B103:G108</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{C4A2DCA3-CD44-4809-824F-F947229E48E5}">
+            <x14:dataBar minLength="0" maxLength="100" gradient="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>B115:G119</xm:sqref>
+        </x14:conditionalFormatting>
+      </x14:conditionalFormattings>
+    </ext>
+  </extLst>
 </worksheet>
 </file>